--- a/publiclogic/docs/canon/PublicLogic_Series1_Final_Workbook.xlsx
+++ b/publiclogic/docs/canon/PublicLogic_Series1_Final_Workbook.xlsx
@@ -5287,7 +5287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="30" min="1" max="1"/>
@@ -5626,6 +5626,50 @@
       <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Moat</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Bookend Rule</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Entry Surface + Repository</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>PuddleJumper owns exactly two guarantees: the Entry Surface (work becomes a CaseSpace: received → logged) and the Repository (work becomes a sealed, append-only record: closed → sealed → rolled up). Everything between belongs to the operator.</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Foundational</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Agnostic Middle Rule</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Content-agnostic, governance-aware</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>The middle is where the operator works, with whatever systems, data, vendors, and processes fit. PJ governs the movement of the CaseSpace, not the software being used; every transition is wrapped by CAL.</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Foundational</t>
         </is>
       </c>
     </row>

--- a/publiclogic/docs/canon/PublicLogic_Series1_Final_Workbook.xlsx
+++ b/publiclogic/docs/canon/PublicLogic_Series1_Final_Workbook.xlsx
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>PuddleJumper owns exactly two guarantees: the Entry Surface (work becomes a CaseSpace: received → logged) and the Repository (work becomes a sealed, append-only record: closed → sealed → rolled up). Everything between belongs to the operator.</t>
+          <t>PuddleJumper owns exactly two guarantees: the Entry Surface (work becomes a CaseSpace: received → logged) and the Repository (work becomes a sealed, append-only record: PRR closed = state, ARCHIEVE seal = operation, parent rollup = view). Everything between belongs to the operator.</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">

--- a/publiclogic/docs/canon/PublicLogic_Series1_Final_Workbook.xlsx
+++ b/publiclogic/docs/canon/PublicLogic_Series1_Final_Workbook.xlsx
@@ -5287,7 +5287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="30" min="1" max="1"/>
@@ -5670,6 +5670,28 @@
       <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Foundational</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Signal Behavior Rule</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Tool-agnostic intake, rule-aware behavior</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>PJ does not care what tool produced the signal (form, email, call, upload, PMS event, calendar, invoice, photo, spreadsheet). It cares what the signal becomes once it is a CaseSpace: a fact, a missing item, a decision, a proof event, a transitory reference, or a sealed record. Classification is recommended by rule and ratified by an authorized user.</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
         </is>
       </c>
     </row>
